--- a/data/database/dimensions.xlsx
+++ b/data/database/dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,36 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RBD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Codigo de escuela</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-02-03 23:33:52</t>
         </is>
       </c>
     </row>

--- a/data/database/dimensions.xlsx
+++ b/data/database/dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RBD</t>
+          <t>Establecimiento</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,59 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-03 23:33:52</t>
+          <t>2026-02-03 23:55:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-02-03 23:55:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Curso</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-02-03 23:56:22</t>
         </is>
       </c>
     </row>

--- a/data/database/dimensions.xlsx
+++ b/data/database/dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,14 +479,10 @@
           <t>list</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Codigo de escuela</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-03 23:55:48</t>
+          <t>2026-02-12 12:05:50</t>
         </is>
       </c>
     </row>
@@ -538,7 +534,141 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-03 23:56:22</t>
+          <t>2026-02-13 09:59:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RUT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rut en formato texto, sin puntos</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-02-13 10:33:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-02-13 10:33:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Asignatura</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-02-13 10:01:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-02-13 10:01:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N Prueba</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-02-13 10:03:04</t>
         </is>
       </c>
     </row>

--- a/data/database/dimensions.xlsx
+++ b/data/database/dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,84 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pregunta</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Habilidad</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-02 15:19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Eje Temático</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-02 15:19:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/dimensions.xlsx
+++ b/data/database/dimensions.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,6 +754,126 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hito</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="2" t="n">
+        <v>46093.54063716435</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nivel</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" s="2" t="n">
+        <v>46093.54063716435</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N Pregunta</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" s="2" t="n">
+        <v>46093.54595423849</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N OA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" s="2" t="n">
+        <v>46093.54595423849</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" s="2" t="n">
+        <v>46093.54595423849</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/dimensions.xlsx
+++ b/data/database/dimensions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,7 +823,7 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>46093.54595423849</v>
+        <v>46093.54595423611</v>
       </c>
     </row>
     <row r="16">
@@ -847,7 +847,7 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>46093.54595423849</v>
+        <v>46093.54595423611</v>
       </c>
     </row>
     <row r="17">
@@ -871,7 +871,63 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>46093.54595423849</v>
+        <v>46093.54595423611</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Evaluación</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:23:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>20</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Entero, análogo a N Prueba</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:29:36</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/database/dimensions.xlsx
+++ b/data/database/dimensions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,6 +930,32 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>21</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:48:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
